--- a/pcb-vendors/pcbway/lpddr4-testbed/lpddr4-testbed-bom.xlsx
+++ b/pcb-vendors/pcbway/lpddr4-testbed/lpddr4-testbed-bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,57 +861,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TP1,TP2,TP3</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TP_0.75mm_SMD</t>
+          <t>MT53E1G32D2NP-046</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>antmicro-footprints:TP_SMD_0.75mm</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>antmicro-footprints:BGA-264-200_10x14.5mm_Layout12x22_P0.8x0.65mm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MT53E1G32D2NP-046 WT:A</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.micron.com/products/dram/lpdram/part-catalog/mt53e1g32d2np-046-wt</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>no physical part - do not order</t>
+          <t>consign - DRAM not in JLCPCB SMT library</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MT53E1G32D2NP-046</t>
+          <t>TPS613221A_SOT-23-5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>antmicro-footprints:BGA-264-200_10x14.5mm_Layout12x22_P0.8x0.65mm</t>
+          <t>antmicro-footprints:SOT-23-5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MT53E1G32D2NP-046 WT:A</t>
+          <t>TPS613221ADBVT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -920,53 +932,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.micron.com/products/dram/lpdram/part-catalog/mt53e1g32d2np-046-wt</t>
+          <t>https://www.ti.com/lit/ds/symlink/tps61322.pdf?ts=1679307661323&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fproduct%252FTPS61322%252Fpart-details%252FTPS613221ADBVT%253Futm_source%253Dgoogle%2526utm_medium%253Dcpc%2526utm_campaign%253Docb-tistore-promo-app_opn_en-cpc-storeic-google-wwe%2526utm_content%253DDevice%2526ds_k%253DTPS613221ADBVT%2526DCM%253Dyes%2526gclid%253DCjwKCAjwiOCgBhAgEiwAjv5whAbq73RvnAdgvLpW8LFuSFEla1kNqoJei2y0mTqS4-Xlc-1KWPDvLxoCIUoQAvD_BwE%2526gclsrc%253Daw.ds</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>consign - DRAM not in JLCPCB SMT library</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TPS613221A_SOT-23-5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>antmicro-footprints:SOT-23-5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TPS613221ADBVT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.ti.com/lit/ds/symlink/tps61322.pdf?ts=1679307661323&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fproduct%252FTPS61322%252Fpart-details%252FTPS613221ADBVT%253Futm_source%253Dgoogle%2526utm_medium%253Dcpc%2526utm_campaign%253Docb-tistore-promo-app_opn_en-cpc-storeic-google-wwe%2526utm_content%253DDevice%2526ds_k%253DTPS613221ADBVT%2526DCM%253Dyes%2526gclid%253DCjwKCAjwiOCgBhAgEiwAjv5whAbq73RvnAdgvLpW8LFuSFEla1kNqoJei2y0mTqS4-Xlc-1KWPDvLxoCIUoQAvD_BwE%2526gclsrc%253Daw.ds</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
